--- a/commission/megan/2026-08.xlsx
+++ b/commission/megan/2026-08.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -37,6 +37,12 @@
     <t>Q3 Route C Accelerator — tiered on invoiced revenue when $30K gate met (else standard waterfall)</t>
   </si>
   <si>
+    <t>Basis</t>
+  </si>
+  <si>
+    <t>✅ CRM + QuickBooks reconciled (paid on cleared)</t>
+  </si>
+  <si>
     <t>Route C — Q3 Accelerator</t>
   </si>
   <si>
@@ -55,13 +61,13 @@
     <t>Growth above baseline (12.5%)</t>
   </si>
   <si>
-    <t>on $5,766.67 collected</t>
+    <t>on $5,366.67 collected</t>
   </si>
   <si>
     <t>Baseline reorders (10%)</t>
   </si>
   <si>
-    <t>on $833.33 collected</t>
+    <t>on $633.33 collected</t>
   </si>
   <si>
     <t>Spiff — 2 new acct(s) × $750</t>
@@ -73,7 +79,7 @@
     <t>vs. standard waterfall would have paid</t>
   </si>
   <si>
-    <t>Uplift: $1854.17</t>
+    <t>Uplift: $2054.17</t>
   </si>
   <si>
     <t>Account / Date</t>
@@ -100,18 +106,12 @@
     <t>Comm Total</t>
   </si>
   <si>
-    <t>Equine Sports Medicine</t>
+    <t>Stahl Veterinary PLLC</t>
   </si>
   <si>
     <t>Payment</t>
   </si>
   <si>
-    <t>ORD-EPL-1141</t>
-  </si>
-  <si>
-    <t>Stahl Veterinary PLLC</t>
-  </si>
-  <si>
     <t>ORD-EPL-1167</t>
   </si>
   <si>
@@ -155,12 +155,6 @@
   </si>
   <si>
     <t>ORD-EPL-1108</t>
-  </si>
-  <si>
-    <t>Signature S Equine</t>
-  </si>
-  <si>
-    <t>ORD-EPL-1171</t>
   </si>
   <si>
     <t>Fairfield Equine Associates</t>
@@ -214,6 +208,11 @@
     <font>
       <b/>
       <color rgb="0F5E4F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="0F5E4F"/>
       <sz val="12"/>
     </font>
     <font>
@@ -242,11 +241,6 @@
     <font>
       <b/>
       <color rgb="FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="0F5E4F"/>
       <sz val="10"/>
     </font>
     <font>
@@ -291,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -299,23 +293,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -675,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -696,7 +691,7 @@
         <v>1</v>
       </c>
       <c r="H1" s="3">
-        <v>3114.17</v>
+        <v>3044.17</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -721,467 +716,413 @@
         <v>7</v>
       </c>
     </row>
+    <row r="4" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>8</v>
+      <c r="A5" s="7" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7">
-        <v>36600</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="B6" s="8">
+        <v>31275</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="9">
+        <v>13</v>
+      </c>
+      <c r="B7" s="10">
         <v>810</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>12</v>
+      <c r="C7" s="11" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="9">
-        <v>720.83</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="B8" s="10">
+        <v>670.83</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="9">
-        <v>83.33</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="B9" s="10">
+        <v>63.33</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="9">
+        <v>19</v>
+      </c>
+      <c r="B10" s="10">
         <v>1500</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="9">
+        <v>20</v>
+      </c>
+      <c r="B11" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="11">
-        <v>1260</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>20</v>
+      <c r="A12" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="12">
+        <v>990</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="13" t="s">
+      <c r="A14" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="C14" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="D14" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="E14" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="F14" s="15" t="s">
         <v>28</v>
       </c>
+      <c r="G14" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="16">
+      <c r="A15" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="17">
         <v>4800</v>
       </c>
-      <c r="H15" s="17">
-        <v>480</v>
+      <c r="H15" s="18">
+        <v>720</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="18">
+      <c r="B16" s="19">
+        <v>46245.5</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="21">
+        <v>4800</v>
+      </c>
+      <c r="G16" s="22">
+        <v>0.15</v>
+      </c>
+      <c r="H16" s="23">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="17">
+        <v>4200</v>
+      </c>
+      <c r="H18" s="18">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="19">
+        <v>46251.5</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="21">
+        <v>4200</v>
+      </c>
+      <c r="G19" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="H19" s="23">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="17">
+        <v>3000</v>
+      </c>
+      <c r="H21" s="18">
+        <v>366.67</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="19">
+        <v>46253.5</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="21">
+        <v>1200</v>
+      </c>
+      <c r="G22" s="22">
+        <v>0.12222222222222222</v>
+      </c>
+      <c r="H22" s="23">
+        <v>146.67</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="19">
+        <v>46259.5</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="21">
+        <v>1800</v>
+      </c>
+      <c r="G23" s="22">
+        <v>0.12222222222222222</v>
+      </c>
+      <c r="H23" s="23">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="17">
+        <v>2400</v>
+      </c>
+      <c r="H25" s="18">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="19">
+        <v>46251.5</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="21">
+        <v>2400</v>
+      </c>
+      <c r="G26" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="H26" s="23">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" s="17">
+        <v>1800</v>
+      </c>
+      <c r="H28" s="18">
+        <v>222.5</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="19">
+        <v>46246.5</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="21">
+        <v>1800</v>
+      </c>
+      <c r="G29" s="22">
+        <v>0.12361111111111112</v>
+      </c>
+      <c r="H29" s="23">
+        <v>222.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" s="17">
+        <v>1800</v>
+      </c>
+      <c r="H31" s="18">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="19">
+        <v>46262.5</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F32" s="21">
+        <v>1800</v>
+      </c>
+      <c r="G32" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="H32" s="23">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F34" s="17">
+        <v>1200</v>
+      </c>
+      <c r="H34" s="18">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="19">
+        <v>46255.5</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F35" s="21">
+        <v>600</v>
+      </c>
+      <c r="G35" s="22">
+        <v>0.12083333333333333</v>
+      </c>
+      <c r="H35" s="23">
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="19">
+        <v>46260.5</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F36" s="21">
+        <v>600</v>
+      </c>
+      <c r="G36" s="22">
+        <v>0.12083333333333333</v>
+      </c>
+      <c r="H36" s="23">
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" s="17">
+        <v>600</v>
+      </c>
+      <c r="H38" s="18">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="19">
         <v>46244.5</v>
       </c>
-      <c r="C16" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="20">
-        <v>4800</v>
-      </c>
-      <c r="G16" s="21">
-        <v>0.1</v>
-      </c>
-      <c r="H16" s="22">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+      <c r="C39" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="16">
-        <v>4800</v>
-      </c>
-      <c r="H18" s="17">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="18">
-        <v>46245.5</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="20">
-        <v>4800</v>
-      </c>
-      <c r="G19" s="21">
+      <c r="E39" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F39" s="21">
+        <v>600</v>
+      </c>
+      <c r="G39" s="22">
         <v>0.15</v>
       </c>
-      <c r="H19" s="22">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="16">
-        <v>4200</v>
-      </c>
-      <c r="H21" s="17">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="18">
-        <v>46251.5</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22" s="20">
-        <v>4200</v>
-      </c>
-      <c r="G22" s="21">
-        <v>0.1</v>
-      </c>
-      <c r="H22" s="22">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" s="16">
-        <v>3000</v>
-      </c>
-      <c r="H24" s="17">
-        <v>366.67</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="18">
-        <v>46253.5</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F25" s="20">
-        <v>1200</v>
-      </c>
-      <c r="G25" s="21">
-        <v>0.12222222222222222</v>
-      </c>
-      <c r="H25" s="22">
-        <v>146.67</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="18">
-        <v>46259.5</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="20">
-        <v>1800</v>
-      </c>
-      <c r="G26" s="21">
-        <v>0.12222222222222222</v>
-      </c>
-      <c r="H26" s="22">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="F28" s="16">
-        <v>2400</v>
-      </c>
-      <c r="H28" s="17">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="18">
-        <v>46251.5</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F29" s="20">
-        <v>2400</v>
-      </c>
-      <c r="G29" s="21">
-        <v>0.1</v>
-      </c>
-      <c r="H29" s="22">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F31" s="16">
-        <v>1800</v>
-      </c>
-      <c r="H31" s="17">
-        <v>222.5</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="18">
-        <v>46246.5</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F32" s="20">
-        <v>1800</v>
-      </c>
-      <c r="G32" s="21">
-        <v>0.12361111111111112</v>
-      </c>
-      <c r="H32" s="22">
-        <v>222.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F34" s="16">
-        <v>1800</v>
-      </c>
-      <c r="H34" s="17">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="18">
-        <v>46262.5</v>
-      </c>
-      <c r="C35" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F35" s="20">
-        <v>1800</v>
-      </c>
-      <c r="G35" s="21">
-        <v>0.1</v>
-      </c>
-      <c r="H35" s="22">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F37" s="16">
-        <v>1200</v>
-      </c>
-      <c r="H37" s="17">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="18">
-        <v>46255.5</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F38" s="20">
-        <v>600</v>
-      </c>
-      <c r="G38" s="21">
-        <v>0.12083333333333333</v>
-      </c>
-      <c r="H38" s="22">
-        <v>72.5</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="18">
-        <v>46260.5</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F39" s="20">
-        <v>600</v>
-      </c>
-      <c r="G39" s="21">
-        <v>0.12083333333333333</v>
-      </c>
-      <c r="H39" s="22">
-        <v>72.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="F41" s="16">
-        <v>600</v>
-      </c>
-      <c r="H41" s="17">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B42" s="18">
-        <v>46241.5</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F42" s="20">
-        <v>600</v>
-      </c>
-      <c r="G42" s="21">
-        <v>0.11666666666666667</v>
-      </c>
-      <c r="H42" s="22">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
+      <c r="H39" s="23">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="F44" s="16">
-        <v>600</v>
-      </c>
-      <c r="H44" s="17">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="18">
-        <v>46244.5</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F45" s="20">
-        <v>600</v>
-      </c>
-      <c r="G45" s="21">
-        <v>0.15</v>
-      </c>
-      <c r="H45" s="22">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="F48" s="24">
-        <v>36600</v>
-      </c>
-      <c r="H48" s="25">
-        <v>3114.17</v>
+      <c r="F42" s="25">
+        <v>31275</v>
+      </c>
+      <c r="H42" s="26">
+        <v>3044.17</v>
       </c>
     </row>
   </sheetData>

--- a/commission/megan/2026-08.xlsx
+++ b/commission/megan/2026-08.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="55">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -61,13 +61,13 @@
     <t>Growth above baseline (12.5%)</t>
   </si>
   <si>
-    <t>on $5,366.67 collected</t>
+    <t>on $5,766.67 collected</t>
   </si>
   <si>
     <t>Baseline reorders (10%)</t>
   </si>
   <si>
-    <t>on $633.33 collected</t>
+    <t>on $833.33 collected</t>
   </si>
   <si>
     <t>Spiff — 2 new acct(s) × $750</t>
@@ -79,7 +79,7 @@
     <t>vs. standard waterfall would have paid</t>
   </si>
   <si>
-    <t>Uplift: $2054.17</t>
+    <t>Uplift: $1854.17</t>
   </si>
   <si>
     <t>Account / Date</t>
@@ -106,12 +106,18 @@
     <t>Comm Total</t>
   </si>
   <si>
+    <t>Equine Sports Medicine</t>
+  </si>
+  <si>
+    <t>Payment</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1141</t>
+  </si>
+  <si>
     <t>Stahl Veterinary PLLC</t>
   </si>
   <si>
-    <t>Payment</t>
-  </si>
-  <si>
     <t>ORD-EPL-1167</t>
   </si>
   <si>
@@ -155,6 +161,12 @@
   </si>
   <si>
     <t>ORD-EPL-1108</t>
+  </si>
+  <si>
+    <t>Signature S Equine</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1171</t>
   </si>
   <si>
     <t>Fairfield Equine Associates</t>
@@ -670,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -691,7 +703,7 @@
         <v>1</v>
       </c>
       <c r="H1" s="3">
-        <v>3044.17</v>
+        <v>3114.17</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -756,7 +768,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="10">
-        <v>670.83</v>
+        <v>720.83</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>16</v>
@@ -767,7 +779,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="10">
-        <v>63.33</v>
+        <v>83.33</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>18</v>
@@ -794,7 +806,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="12">
-        <v>990</v>
+        <v>1260</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>22</v>
@@ -834,12 +846,12 @@
         <v>4800</v>
       </c>
       <c r="H15" s="18">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="19">
-        <v>46245.5</v>
+        <v>46244.5</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>32</v>
@@ -851,10 +863,10 @@
         <v>4800</v>
       </c>
       <c r="G16" s="22">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="H16" s="23">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -862,15 +874,15 @@
         <v>34</v>
       </c>
       <c r="F18" s="17">
-        <v>4200</v>
+        <v>4800</v>
       </c>
       <c r="H18" s="18">
-        <v>420</v>
+        <v>720</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="19">
-        <v>46251.5</v>
+        <v>46245.5</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>32</v>
@@ -879,13 +891,13 @@
         <v>35</v>
       </c>
       <c r="F19" s="21">
-        <v>4200</v>
+        <v>4800</v>
       </c>
       <c r="G19" s="22">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="H19" s="23">
-        <v>420</v>
+        <v>720</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -893,15 +905,15 @@
         <v>36</v>
       </c>
       <c r="F21" s="17">
-        <v>3000</v>
+        <v>4200</v>
       </c>
       <c r="H21" s="18">
-        <v>366.67</v>
+        <v>420</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="19">
-        <v>46253.5</v>
+        <v>46251.5</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>32</v>
@@ -910,49 +922,49 @@
         <v>37</v>
       </c>
       <c r="F22" s="21">
+        <v>4200</v>
+      </c>
+      <c r="G22" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="H22" s="23">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="17">
+        <v>3000</v>
+      </c>
+      <c r="H24" s="18">
+        <v>366.67</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="19">
+        <v>46253.5</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="21">
         <v>1200</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G25" s="22">
         <v>0.12222222222222222</v>
       </c>
-      <c r="H22" s="23">
+      <c r="H25" s="23">
         <v>146.67</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="19">
-        <v>46259.5</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="21">
-        <v>1800</v>
-      </c>
-      <c r="G23" s="22">
-        <v>0.12222222222222222</v>
-      </c>
-      <c r="H23" s="23">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="17">
-        <v>2400</v>
-      </c>
-      <c r="H25" s="18">
-        <v>240</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="19">
-        <v>46251.5</v>
+        <v>46259.5</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>32</v>
@@ -961,13 +973,13 @@
         <v>40</v>
       </c>
       <c r="F26" s="21">
-        <v>2400</v>
+        <v>1800</v>
       </c>
       <c r="G26" s="22">
-        <v>0.1</v>
+        <v>0.12222222222222222</v>
       </c>
       <c r="H26" s="23">
-        <v>240</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -975,15 +987,15 @@
         <v>41</v>
       </c>
       <c r="F28" s="17">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="H28" s="18">
-        <v>222.5</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="19">
-        <v>46246.5</v>
+        <v>46251.5</v>
       </c>
       <c r="C29" s="20" t="s">
         <v>32</v>
@@ -992,13 +1004,13 @@
         <v>42</v>
       </c>
       <c r="F29" s="21">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="G29" s="22">
-        <v>0.12361111111111112</v>
+        <v>0.1</v>
       </c>
       <c r="H29" s="23">
-        <v>222.5</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1009,12 +1021,12 @@
         <v>1800</v>
       </c>
       <c r="H31" s="18">
-        <v>180</v>
+        <v>222.5</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="19">
-        <v>46262.5</v>
+        <v>46246.5</v>
       </c>
       <c r="C32" s="20" t="s">
         <v>32</v>
@@ -1026,10 +1038,10 @@
         <v>1800</v>
       </c>
       <c r="G32" s="22">
-        <v>0.1</v>
+        <v>0.12361111111111112</v>
       </c>
       <c r="H32" s="23">
-        <v>180</v>
+        <v>222.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1037,15 +1049,15 @@
         <v>45</v>
       </c>
       <c r="F34" s="17">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="H34" s="18">
-        <v>145</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="19">
-        <v>46255.5</v>
+        <v>46262.5</v>
       </c>
       <c r="C35" s="20" t="s">
         <v>32</v>
@@ -1054,49 +1066,49 @@
         <v>46</v>
       </c>
       <c r="F35" s="21">
+        <v>1800</v>
+      </c>
+      <c r="G35" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="H35" s="23">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F37" s="17">
+        <v>1200</v>
+      </c>
+      <c r="H37" s="18">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" s="19">
+        <v>46255.5</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" s="21">
         <v>600</v>
       </c>
-      <c r="G35" s="22">
+      <c r="G38" s="22">
         <v>0.12083333333333333</v>
       </c>
-      <c r="H35" s="23">
+      <c r="H38" s="23">
         <v>72.5</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="19">
-        <v>46260.5</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F36" s="21">
-        <v>600</v>
-      </c>
-      <c r="G36" s="22">
-        <v>0.12083333333333333</v>
-      </c>
-      <c r="H36" s="23">
-        <v>72.5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="F38" s="17">
-        <v>600</v>
-      </c>
-      <c r="H38" s="18">
-        <v>90</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="19">
-        <v>46244.5</v>
+        <v>46260.5</v>
       </c>
       <c r="C39" s="20" t="s">
         <v>32</v>
@@ -1108,21 +1120,83 @@
         <v>600</v>
       </c>
       <c r="G39" s="22">
+        <v>0.12083333333333333</v>
+      </c>
+      <c r="H39" s="23">
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="F41" s="17">
+        <v>600</v>
+      </c>
+      <c r="H41" s="18">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B42" s="19">
+        <v>46241.5</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F42" s="21">
+        <v>600</v>
+      </c>
+      <c r="G42" s="22">
+        <v>0.11666666666666667</v>
+      </c>
+      <c r="H42" s="23">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F44" s="17">
+        <v>600</v>
+      </c>
+      <c r="H44" s="18">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B45" s="19">
+        <v>46244.5</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F45" s="21">
+        <v>600</v>
+      </c>
+      <c r="G45" s="22">
         <v>0.15</v>
       </c>
-      <c r="H39" s="23">
+      <c r="H45" s="23">
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="F42" s="25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F48" s="25">
         <v>31275</v>
       </c>
-      <c r="H42" s="26">
-        <v>3044.17</v>
+      <c r="H48" s="26">
+        <v>3114.17</v>
       </c>
     </row>
   </sheetData>

--- a/commission/megan/2026-08.xlsx
+++ b/commission/megan/2026-08.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -73,7 +73,13 @@
     <t>Spiff — 2 new acct(s) × $750</t>
   </si>
   <si>
+    <t>Qualifying: Stahl Veterinary PLLC</t>
+  </si>
+  <si>
     <t>Breadth bonus — 4 accts ≥20%</t>
+  </si>
+  <si>
+    <t>Qualifying: Ocala Equine Hospital, East Coast Equine Veterinary, Mountain Pointe Equine, Signature S Equine</t>
   </si>
   <si>
     <t>vs. standard waterfall would have paid</t>
@@ -785,62 +791,78 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="10">
         <v>1500</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" s="10">
         <v>0</v>
       </c>
+      <c r="C11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" s="12">
         <v>1260</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F15" s="17">
         <v>4800</v>
@@ -854,10 +876,10 @@
         <v>46244.5</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F16" s="21">
         <v>4800</v>
@@ -871,7 +893,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F18" s="17">
         <v>4800</v>
@@ -885,10 +907,10 @@
         <v>46245.5</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F19" s="21">
         <v>4800</v>
@@ -902,7 +924,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F21" s="17">
         <v>4200</v>
@@ -916,10 +938,10 @@
         <v>46251.5</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F22" s="21">
         <v>4200</v>
@@ -933,7 +955,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F24" s="17">
         <v>3000</v>
@@ -947,10 +969,10 @@
         <v>46253.5</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F25" s="21">
         <v>1200</v>
@@ -967,10 +989,10 @@
         <v>46259.5</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F26" s="21">
         <v>1800</v>
@@ -984,7 +1006,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F28" s="17">
         <v>2400</v>
@@ -998,10 +1020,10 @@
         <v>46251.5</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F29" s="21">
         <v>2400</v>
@@ -1015,7 +1037,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F31" s="17">
         <v>1800</v>
@@ -1029,10 +1051,10 @@
         <v>46246.5</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F32" s="21">
         <v>1800</v>
@@ -1046,7 +1068,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F34" s="17">
         <v>1800</v>
@@ -1060,10 +1082,10 @@
         <v>46262.5</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F35" s="21">
         <v>1800</v>
@@ -1077,7 +1099,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F37" s="17">
         <v>1200</v>
@@ -1091,10 +1113,10 @@
         <v>46255.5</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F38" s="21">
         <v>600</v>
@@ -1111,10 +1133,10 @@
         <v>46260.5</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F39" s="21">
         <v>600</v>
@@ -1128,7 +1150,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F41" s="17">
         <v>600</v>
@@ -1142,10 +1164,10 @@
         <v>46241.5</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F42" s="21">
         <v>600</v>
@@ -1159,7 +1181,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F44" s="17">
         <v>600</v>
@@ -1173,10 +1195,10 @@
         <v>46244.5</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F45" s="21">
         <v>600</v>
@@ -1190,7 +1212,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F48" s="25">
         <v>31275</v>
@@ -1200,6 +1222,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C11:H11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/commission/megan/2026-08.xlsx
+++ b/commission/megan/2026-08.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="August 2026-08" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Invoiced This Month" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="105">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -182,6 +183,150 @@
   </si>
   <si>
     <t>GRAND TOTAL</t>
+  </si>
+  <si>
+    <t>Invoiced This Month — Megan Smith — August 2026</t>
+  </si>
+  <si>
+    <t>Every invoice you wrote this month (paid or unpaid). Commission math comes from Tab 1 — this sheet is for visibility only.</t>
+  </si>
+  <si>
+    <t>INV#</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Vials</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>Commissionable</t>
+  </si>
+  <si>
+    <t>Paid</t>
+  </si>
+  <si>
+    <t>Payment Date</t>
+  </si>
+  <si>
+    <t>Open Bal</t>
+  </si>
+  <si>
+    <t>Promo</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1168</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>SAMPLE26</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1163</t>
+  </si>
+  <si>
+    <t>Ginn Equine</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1177</t>
+  </si>
+  <si>
+    <t>Equine Services Ltd</t>
+  </si>
+  <si>
+    <t>FREE_VIALS</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1176</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1188</t>
+  </si>
+  <si>
+    <t>Dr. Mark A Christine</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1187</t>
+  </si>
+  <si>
+    <t>Cleveland Equine Clinic LLC</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1186</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1193</t>
+  </si>
+  <si>
+    <t>Virginia Equine Imaging</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1192</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1191</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1194</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1196</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1195</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1200</t>
+  </si>
+  <si>
+    <t>Woodland Run Equine Veterinary</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1199</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1208</t>
+  </si>
+  <si>
+    <t>Peterson Smith Equine Hospital</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1207</t>
+  </si>
+  <si>
+    <t>CINV-EPL-1021</t>
+  </si>
+  <si>
+    <t>VET600</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1203</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1209</t>
+  </si>
+  <si>
+    <t>Colts Neck Equine</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1219</t>
+  </si>
+  <si>
+    <t>Southern Veterinary Clinic</t>
+  </si>
+  <si>
+    <t>25 invoices</t>
   </si>
 </sst>
 </file>
@@ -194,7 +339,7 @@
     <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -271,6 +416,45 @@
     <font>
       <b/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="123F35"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="7A7974"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="DA7101"/>
+    </font>
+    <font>
+      <b/>
+    </font>
+    <font>
+      <color rgb="7A7974"/>
+    </font>
+    <font>
+      <color rgb="964219"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="DA7101"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="123F35"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="0F5E4F"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="964219"/>
     </font>
   </fonts>
   <fills count="4">
@@ -303,7 +487,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -347,6 +531,48 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1229,4 +1455,1059 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="29" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="30">
+        <v>46238.5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="31">
+        <v>2</v>
+      </c>
+      <c r="E6" s="21">
+        <v>1650</v>
+      </c>
+      <c r="F6" s="32">
+        <v>1650</v>
+      </c>
+      <c r="G6" s="33">
+        <v>0</v>
+      </c>
+      <c r="H6" s="21">
+        <v>0</v>
+      </c>
+      <c r="I6" s="34">
+        <v>0</v>
+      </c>
+      <c r="J6" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K6" s="34">
+        <v>0</v>
+      </c>
+      <c r="L6" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="30">
+        <v>46238.5</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="31">
+        <v>8</v>
+      </c>
+      <c r="E7" s="21">
+        <v>6600</v>
+      </c>
+      <c r="F7" s="32">
+        <v>1800</v>
+      </c>
+      <c r="G7" s="33">
+        <v>4800</v>
+      </c>
+      <c r="H7" s="21">
+        <v>4800</v>
+      </c>
+      <c r="I7" s="23">
+        <v>4943.52</v>
+      </c>
+      <c r="J7" s="30">
+        <v>46245.5</v>
+      </c>
+      <c r="K7" s="34">
+        <v>0</v>
+      </c>
+      <c r="L7" s="35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="30">
+        <v>46238.5</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="31">
+        <v>2</v>
+      </c>
+      <c r="E8" s="21">
+        <v>1650</v>
+      </c>
+      <c r="F8" s="32">
+        <v>1650</v>
+      </c>
+      <c r="G8" s="33">
+        <v>0</v>
+      </c>
+      <c r="H8" s="21">
+        <v>0</v>
+      </c>
+      <c r="I8" s="34">
+        <v>0</v>
+      </c>
+      <c r="J8" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K8" s="34">
+        <v>0</v>
+      </c>
+      <c r="L8" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="30">
+        <v>46241.5</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="31">
+        <v>1</v>
+      </c>
+      <c r="E9" s="21">
+        <v>825</v>
+      </c>
+      <c r="F9" s="32">
+        <v>225</v>
+      </c>
+      <c r="G9" s="33">
+        <v>600</v>
+      </c>
+      <c r="H9" s="21">
+        <v>600</v>
+      </c>
+      <c r="I9" s="23">
+        <v>617.94</v>
+      </c>
+      <c r="J9" s="30">
+        <v>46241.5</v>
+      </c>
+      <c r="K9" s="34">
+        <v>0</v>
+      </c>
+      <c r="L9" s="35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" s="30">
+        <v>46245.5</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="31">
+        <v>1</v>
+      </c>
+      <c r="E10" s="21">
+        <v>825</v>
+      </c>
+      <c r="F10" s="32">
+        <v>825</v>
+      </c>
+      <c r="G10" s="33">
+        <v>0</v>
+      </c>
+      <c r="H10" s="21">
+        <v>0</v>
+      </c>
+      <c r="I10" s="34">
+        <v>0</v>
+      </c>
+      <c r="J10" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K10" s="34">
+        <v>0</v>
+      </c>
+      <c r="L10" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="30">
+        <v>46245.5</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="31">
+        <v>3</v>
+      </c>
+      <c r="E11" s="21">
+        <v>2475</v>
+      </c>
+      <c r="F11" s="32">
+        <v>675</v>
+      </c>
+      <c r="G11" s="33">
+        <v>1800</v>
+      </c>
+      <c r="H11" s="21">
+        <v>1800</v>
+      </c>
+      <c r="I11" s="34">
+        <v>0</v>
+      </c>
+      <c r="J11" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K11" s="36">
+        <v>1800</v>
+      </c>
+      <c r="L11" s="35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="30">
+        <v>46246.5</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="31">
+        <v>3</v>
+      </c>
+      <c r="E12" s="21">
+        <v>2475</v>
+      </c>
+      <c r="F12" s="32">
+        <v>675</v>
+      </c>
+      <c r="G12" s="33">
+        <v>1800</v>
+      </c>
+      <c r="H12" s="21">
+        <v>1800</v>
+      </c>
+      <c r="I12" s="23">
+        <v>1853.82</v>
+      </c>
+      <c r="J12" s="30">
+        <v>46246.5</v>
+      </c>
+      <c r="K12" s="34">
+        <v>0</v>
+      </c>
+      <c r="L12" s="35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="30">
+        <v>46248.5</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="31">
+        <v>1</v>
+      </c>
+      <c r="E13" s="21">
+        <v>825</v>
+      </c>
+      <c r="F13" s="32">
+        <v>825</v>
+      </c>
+      <c r="G13" s="33">
+        <v>0</v>
+      </c>
+      <c r="H13" s="21">
+        <v>0</v>
+      </c>
+      <c r="I13" s="34">
+        <v>0</v>
+      </c>
+      <c r="J13" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K13" s="34">
+        <v>0</v>
+      </c>
+      <c r="L13" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="30">
+        <v>46248.5</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="31">
+        <v>2</v>
+      </c>
+      <c r="E14" s="21">
+        <v>1650</v>
+      </c>
+      <c r="F14" s="32">
+        <v>1650</v>
+      </c>
+      <c r="G14" s="33">
+        <v>0</v>
+      </c>
+      <c r="H14" s="21">
+        <v>0</v>
+      </c>
+      <c r="I14" s="34">
+        <v>0</v>
+      </c>
+      <c r="J14" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K14" s="34">
+        <v>0</v>
+      </c>
+      <c r="L14" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="30">
+        <v>46248.5</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="31">
+        <v>4</v>
+      </c>
+      <c r="E15" s="21">
+        <v>3300</v>
+      </c>
+      <c r="F15" s="32">
+        <v>3300</v>
+      </c>
+      <c r="G15" s="33">
+        <v>0</v>
+      </c>
+      <c r="H15" s="21">
+        <v>0</v>
+      </c>
+      <c r="I15" s="34">
+        <v>0</v>
+      </c>
+      <c r="J15" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K15" s="34">
+        <v>0</v>
+      </c>
+      <c r="L15" s="35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="30">
+        <v>46251.5</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="31">
+        <v>1</v>
+      </c>
+      <c r="E16" s="21">
+        <v>825</v>
+      </c>
+      <c r="F16" s="32">
+        <v>225</v>
+      </c>
+      <c r="G16" s="33">
+        <v>600</v>
+      </c>
+      <c r="H16" s="21">
+        <v>600</v>
+      </c>
+      <c r="I16" s="34">
+        <v>0</v>
+      </c>
+      <c r="J16" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K16" s="36">
+        <v>600</v>
+      </c>
+      <c r="L16" s="35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="30">
+        <v>46251.5</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="31">
+        <v>8</v>
+      </c>
+      <c r="E17" s="21">
+        <v>6600</v>
+      </c>
+      <c r="F17" s="32">
+        <v>1800</v>
+      </c>
+      <c r="G17" s="33">
+        <v>4800</v>
+      </c>
+      <c r="H17" s="21">
+        <v>4800</v>
+      </c>
+      <c r="I17" s="23">
+        <v>4800</v>
+      </c>
+      <c r="J17" s="30">
+        <v>46276.5</v>
+      </c>
+      <c r="K17" s="34">
+        <v>0</v>
+      </c>
+      <c r="L17" s="35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="30">
+        <v>46251.5</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="31">
+        <v>4</v>
+      </c>
+      <c r="E18" s="21">
+        <v>3300</v>
+      </c>
+      <c r="F18" s="32">
+        <v>900</v>
+      </c>
+      <c r="G18" s="33">
+        <v>2400</v>
+      </c>
+      <c r="H18" s="21">
+        <v>2400</v>
+      </c>
+      <c r="I18" s="23">
+        <v>2400</v>
+      </c>
+      <c r="J18" s="30">
+        <v>46267.5</v>
+      </c>
+      <c r="K18" s="34">
+        <v>0</v>
+      </c>
+      <c r="L18" s="35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="30">
+        <v>46252.5</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="31">
+        <v>1</v>
+      </c>
+      <c r="E19" s="21">
+        <v>825</v>
+      </c>
+      <c r="F19" s="32">
+        <v>150</v>
+      </c>
+      <c r="G19" s="33">
+        <v>675</v>
+      </c>
+      <c r="H19" s="21">
+        <v>600</v>
+      </c>
+      <c r="I19" s="23">
+        <v>675</v>
+      </c>
+      <c r="J19" s="30">
+        <v>46279.5</v>
+      </c>
+      <c r="K19" s="34">
+        <v>0</v>
+      </c>
+      <c r="L19" s="35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="30">
+        <v>46253.5</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="31">
+        <v>3</v>
+      </c>
+      <c r="E20" s="21">
+        <v>2475</v>
+      </c>
+      <c r="F20" s="32">
+        <v>2475</v>
+      </c>
+      <c r="G20" s="33">
+        <v>0</v>
+      </c>
+      <c r="H20" s="21">
+        <v>0</v>
+      </c>
+      <c r="I20" s="34">
+        <v>0</v>
+      </c>
+      <c r="J20" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K20" s="34">
+        <v>0</v>
+      </c>
+      <c r="L20" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="30">
+        <v>46253.5</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="31">
+        <v>1</v>
+      </c>
+      <c r="E21" s="21">
+        <v>825</v>
+      </c>
+      <c r="F21" s="32">
+        <v>225</v>
+      </c>
+      <c r="G21" s="33">
+        <v>600</v>
+      </c>
+      <c r="H21" s="21">
+        <v>600</v>
+      </c>
+      <c r="I21" s="34">
+        <v>0</v>
+      </c>
+      <c r="J21" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K21" s="36">
+        <v>600</v>
+      </c>
+      <c r="L21" s="35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="30">
+        <v>46254.5</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" s="31">
+        <v>2</v>
+      </c>
+      <c r="E22" s="21">
+        <v>1650</v>
+      </c>
+      <c r="F22" s="32">
+        <v>1650</v>
+      </c>
+      <c r="G22" s="33">
+        <v>0</v>
+      </c>
+      <c r="H22" s="21">
+        <v>0</v>
+      </c>
+      <c r="I22" s="34">
+        <v>0</v>
+      </c>
+      <c r="J22" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K22" s="34">
+        <v>0</v>
+      </c>
+      <c r="L22" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="30">
+        <v>46254.5</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="31">
+        <v>8</v>
+      </c>
+      <c r="E23" s="21">
+        <v>6600</v>
+      </c>
+      <c r="F23" s="32">
+        <v>1800</v>
+      </c>
+      <c r="G23" s="33">
+        <v>4800</v>
+      </c>
+      <c r="H23" s="21">
+        <v>4800</v>
+      </c>
+      <c r="I23" s="34">
+        <v>0</v>
+      </c>
+      <c r="J23" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K23" s="36">
+        <v>4800</v>
+      </c>
+      <c r="L23" s="35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="30">
+        <v>46255.5</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" s="31">
+        <v>2</v>
+      </c>
+      <c r="E24" s="21">
+        <v>1650</v>
+      </c>
+      <c r="F24" s="32">
+        <v>1650</v>
+      </c>
+      <c r="G24" s="33">
+        <v>0</v>
+      </c>
+      <c r="H24" s="21">
+        <v>0</v>
+      </c>
+      <c r="I24" s="34">
+        <v>0</v>
+      </c>
+      <c r="J24" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K24" s="34">
+        <v>0</v>
+      </c>
+      <c r="L24" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="30">
+        <v>46255.5</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" s="31">
+        <v>8</v>
+      </c>
+      <c r="E25" s="21">
+        <v>6600</v>
+      </c>
+      <c r="F25" s="32">
+        <v>1800</v>
+      </c>
+      <c r="G25" s="33">
+        <v>4800</v>
+      </c>
+      <c r="H25" s="21">
+        <v>4800</v>
+      </c>
+      <c r="I25" s="23">
+        <v>4800</v>
+      </c>
+      <c r="J25" s="30">
+        <v>46267.5</v>
+      </c>
+      <c r="K25" s="34">
+        <v>0</v>
+      </c>
+      <c r="L25" s="35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" s="30">
+        <v>46255.5</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26" s="31">
+        <v>5</v>
+      </c>
+      <c r="E26" s="21">
+        <v>3000</v>
+      </c>
+      <c r="F26" s="34">
+        <v>0</v>
+      </c>
+      <c r="G26" s="33">
+        <v>3000</v>
+      </c>
+      <c r="H26" s="21">
+        <v>3000</v>
+      </c>
+      <c r="I26" s="34">
+        <v>0</v>
+      </c>
+      <c r="J26" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K26" s="36">
+        <v>3000</v>
+      </c>
+      <c r="L26" s="35" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="30">
+        <v>46255.5</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="31">
+        <v>1</v>
+      </c>
+      <c r="E27" s="21">
+        <v>825</v>
+      </c>
+      <c r="F27" s="32">
+        <v>825</v>
+      </c>
+      <c r="G27" s="33">
+        <v>0</v>
+      </c>
+      <c r="H27" s="21">
+        <v>0</v>
+      </c>
+      <c r="I27" s="34">
+        <v>0</v>
+      </c>
+      <c r="J27" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K27" s="34">
+        <v>0</v>
+      </c>
+      <c r="L27" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="30">
+        <v>46255.5</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="31">
+        <v>1</v>
+      </c>
+      <c r="E28" s="21">
+        <v>825</v>
+      </c>
+      <c r="F28" s="32">
+        <v>225</v>
+      </c>
+      <c r="G28" s="33">
+        <v>600</v>
+      </c>
+      <c r="H28" s="21">
+        <v>600</v>
+      </c>
+      <c r="I28" s="23">
+        <v>617.94</v>
+      </c>
+      <c r="J28" s="30">
+        <v>46255.5</v>
+      </c>
+      <c r="K28" s="34">
+        <v>0</v>
+      </c>
+      <c r="L28" s="35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" s="30">
+        <v>46258.5</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" s="31">
+        <v>1</v>
+      </c>
+      <c r="E29" s="21">
+        <v>825</v>
+      </c>
+      <c r="F29" s="32">
+        <v>825</v>
+      </c>
+      <c r="G29" s="33">
+        <v>0</v>
+      </c>
+      <c r="H29" s="21">
+        <v>0</v>
+      </c>
+      <c r="I29" s="34">
+        <v>0</v>
+      </c>
+      <c r="J29" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K29" s="34">
+        <v>0</v>
+      </c>
+      <c r="L29" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="30">
+        <v>46262.5</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D30" s="31">
+        <v>1</v>
+      </c>
+      <c r="E30" s="21">
+        <v>825</v>
+      </c>
+      <c r="F30" s="32">
+        <v>825</v>
+      </c>
+      <c r="G30" s="33">
+        <v>0</v>
+      </c>
+      <c r="H30" s="21">
+        <v>0</v>
+      </c>
+      <c r="I30" s="34">
+        <v>0</v>
+      </c>
+      <c r="J30" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K30" s="34">
+        <v>0</v>
+      </c>
+      <c r="L30" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="38">
+        <v>74</v>
+      </c>
+      <c r="E32" s="33">
+        <v>59925</v>
+      </c>
+      <c r="F32" s="39">
+        <v>28650</v>
+      </c>
+      <c r="G32" s="40">
+        <v>31275</v>
+      </c>
+      <c r="H32" s="33">
+        <v>31200</v>
+      </c>
+      <c r="I32" s="41">
+        <v>20708.219999999998</v>
+      </c>
+      <c r="K32" s="42">
+        <v>10800</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/commission/megan/2026-08.xlsx
+++ b/commission/megan/2026-08.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="104">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -26,7 +26,7 @@
     <t>Due By</t>
   </si>
   <si>
-    <t>September 30, 2026</t>
+    <t>2026-09-30</t>
   </si>
   <si>
     <t>August 2026 | Megan Smith</t>
@@ -38,12 +38,6 @@
     <t>Q3 Route C Accelerator — tiered on invoiced revenue when $30K gate met (else standard waterfall)</t>
   </si>
   <si>
-    <t>Basis</t>
-  </si>
-  <si>
-    <t>✅ CRM + QuickBooks reconciled (paid on cleared)</t>
-  </si>
-  <si>
     <t>Route C — Q3 Accelerator</t>
   </si>
   <si>
@@ -56,37 +50,40 @@
     <t>New / Reactivated (15%)</t>
   </si>
   <si>
-    <t>on $5,400.00 collected</t>
+    <t>on $15,000.00 collected</t>
   </si>
   <si>
     <t>Growth above baseline (12.5%)</t>
   </si>
   <si>
-    <t>on $5,766.67 collected</t>
+    <t>on $10,200.00 collected</t>
   </si>
   <si>
     <t>Baseline reorders (10%)</t>
   </si>
   <si>
-    <t>on $833.33 collected</t>
-  </si>
-  <si>
-    <t>Spiff — 2 new acct(s) × $750</t>
-  </si>
-  <si>
-    <t>Qualifying: Stahl Veterinary PLLC</t>
-  </si>
-  <si>
-    <t>Breadth bonus — 4 accts ≥20%</t>
-  </si>
-  <si>
-    <t>Qualifying: Ocala Equine Hospital, East Coast Equine Veterinary, Mountain Pointe Equine, Signature S Equine</t>
-  </si>
-  <si>
-    <t>vs. standard waterfall would have paid</t>
-  </si>
-  <si>
-    <t>Uplift: $1854.17</t>
+    <t>on $0.00 collected</t>
+  </si>
+  <si>
+    <t>Spiff — 3 new acct(s) × $750</t>
+  </si>
+  <si>
+    <t>Earned on 2026-08 invoicing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      • Stahl Veterinary PLLC (inv 2026-08-04, ORD-EPL-1167)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      • Cleveland Equine Clinic LLC (inv 2026-08-17, ORD-EPL-1192)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      • Running S Equine (ORD-EPL-1130) — CEO override: CEO one-time approval: 8 vials in Q3 (7 in Jul + 1 pre-Q3), account is effectively new to volume</t>
+  </si>
+  <si>
+    <t>Breadth bonus — 0 accts ≥20% above baseline</t>
+  </si>
+  <si>
+    <t>Only 0 of 5 needed — no bonus this month</t>
   </si>
   <si>
     <t>Account / Date</t>
@@ -339,7 +336,7 @@
     <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -371,11 +368,6 @@
     <font>
       <b/>
       <color rgb="0F5E4F"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="0F5E4F"/>
       <sz val="12"/>
     </font>
     <font>
@@ -402,8 +394,18 @@
       <sz val="10"/>
     </font>
     <font>
+      <i/>
+      <color rgb="7A5C1C"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="0F5E4F"/>
       <sz val="10"/>
     </font>
     <font>
@@ -487,7 +489,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -495,12 +497,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -508,33 +509,33 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -544,26 +545,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -573,6 +571,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -914,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -935,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="H1" s="3">
-        <v>3114.17</v>
+        <v>5775</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -960,497 +961,517 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G4" s="2" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="8">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7">
         <v>31275</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>12</v>
+      <c r="C6" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="10">
-        <v>810</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="B7" s="9">
+        <v>2250</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="10">
-        <v>720.83</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="B8" s="9">
+        <v>1275</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="10">
-        <v>83.33</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="B9" s="9">
+        <v>0</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="9">
+        <v>2250</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="10">
-        <v>1500</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="10">
-        <v>0</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="9">
+        <v>0</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="12">
-        <v>1260</v>
-      </c>
-      <c r="C12" s="13" t="s">
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="C16" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="D16" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="E16" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="F16" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="G16" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="H16" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="15" t="s">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="F17" s="16">
+        <v>4800</v>
+      </c>
+      <c r="H17" s="17">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="18">
+        <v>46244.5</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="17">
+      <c r="E18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="20">
         <v>4800</v>
       </c>
-      <c r="H15" s="18">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="19">
+      <c r="G18" s="21">
+        <v>0.15</v>
+      </c>
+      <c r="H18" s="22">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" s="16">
+        <v>4800</v>
+      </c>
+      <c r="H20" s="17">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="18">
+        <v>46245.5</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="20">
+        <v>4800</v>
+      </c>
+      <c r="G21" s="21">
+        <v>0.15</v>
+      </c>
+      <c r="H21" s="22">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="16">
+        <v>4200</v>
+      </c>
+      <c r="H23" s="17">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="18">
+        <v>46251.5</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="20">
+        <v>4200</v>
+      </c>
+      <c r="G24" s="21">
+        <v>0.125</v>
+      </c>
+      <c r="H24" s="22">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="16">
+        <v>3000</v>
+      </c>
+      <c r="H26" s="17">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="18">
+        <v>46253.5</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="20">
+        <v>1200</v>
+      </c>
+      <c r="G27" s="21">
+        <v>0.125</v>
+      </c>
+      <c r="H27" s="22">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="18">
+        <v>46259.5</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" s="20">
+        <v>1800</v>
+      </c>
+      <c r="G28" s="21">
+        <v>0.125</v>
+      </c>
+      <c r="H28" s="22">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="16">
+        <v>2400</v>
+      </c>
+      <c r="H30" s="17">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="18">
+        <v>46251.5</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" s="20">
+        <v>2400</v>
+      </c>
+      <c r="G31" s="21">
+        <v>0.15</v>
+      </c>
+      <c r="H31" s="22">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" s="16">
+        <v>1800</v>
+      </c>
+      <c r="H33" s="17">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="18">
+        <v>46246.5</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F34" s="20">
+        <v>1800</v>
+      </c>
+      <c r="G34" s="21">
+        <v>0.125</v>
+      </c>
+      <c r="H34" s="22">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F36" s="16">
+        <v>1800</v>
+      </c>
+      <c r="H36" s="17">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37" s="18">
+        <v>46262.5</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F37" s="20">
+        <v>1800</v>
+      </c>
+      <c r="G37" s="21">
+        <v>0.15</v>
+      </c>
+      <c r="H37" s="22">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F39" s="16">
+        <v>1200</v>
+      </c>
+      <c r="H39" s="17">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="18">
+        <v>46255.5</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F40" s="20">
+        <v>600</v>
+      </c>
+      <c r="G40" s="21">
+        <v>0.125</v>
+      </c>
+      <c r="H40" s="22">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="18">
+        <v>46260.5</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F41" s="20">
+        <v>600</v>
+      </c>
+      <c r="G41" s="21">
+        <v>0.15</v>
+      </c>
+      <c r="H41" s="22">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F43" s="16">
+        <v>600</v>
+      </c>
+      <c r="H43" s="17">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B44" s="18">
+        <v>46241.5</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F44" s="20">
+        <v>600</v>
+      </c>
+      <c r="G44" s="21">
+        <v>0.125</v>
+      </c>
+      <c r="H44" s="22">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" s="16">
+        <v>600</v>
+      </c>
+      <c r="H46" s="17">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B47" s="18">
         <v>46244.5</v>
       </c>
-      <c r="C16" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" s="21">
-        <v>4800</v>
-      </c>
-      <c r="G16" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="H16" s="23">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="17">
-        <v>4800</v>
-      </c>
-      <c r="H18" s="18">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="19">
-        <v>46245.5</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F19" s="21">
-        <v>4800</v>
-      </c>
-      <c r="G19" s="22">
+      <c r="C47" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F47" s="20">
+        <v>600</v>
+      </c>
+      <c r="G47" s="21">
         <v>0.15</v>
       </c>
-      <c r="H19" s="23">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="17">
-        <v>4200</v>
-      </c>
-      <c r="H21" s="18">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="19">
-        <v>46251.5</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="21">
-        <v>4200</v>
-      </c>
-      <c r="G22" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="H22" s="23">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="F24" s="17">
-        <v>3000</v>
-      </c>
-      <c r="H24" s="18">
-        <v>366.67</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="19">
-        <v>46253.5</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F25" s="21">
-        <v>1200</v>
-      </c>
-      <c r="G25" s="22">
-        <v>0.12222222222222222</v>
-      </c>
-      <c r="H25" s="23">
-        <v>146.67</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="19">
-        <v>46259.5</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" s="21">
-        <v>1800</v>
-      </c>
-      <c r="G26" s="22">
-        <v>0.12222222222222222</v>
-      </c>
-      <c r="H26" s="23">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="17">
-        <v>2400</v>
-      </c>
-      <c r="H28" s="18">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="19">
-        <v>46251.5</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F29" s="21">
-        <v>2400</v>
-      </c>
-      <c r="G29" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="H29" s="23">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F31" s="17">
-        <v>1800</v>
-      </c>
-      <c r="H31" s="18">
-        <v>222.5</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="19">
-        <v>46246.5</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F32" s="21">
-        <v>1800</v>
-      </c>
-      <c r="G32" s="22">
-        <v>0.12361111111111112</v>
-      </c>
-      <c r="H32" s="23">
-        <v>222.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="F34" s="17">
-        <v>1800</v>
-      </c>
-      <c r="H34" s="18">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="19">
-        <v>46262.5</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F35" s="21">
-        <v>1800</v>
-      </c>
-      <c r="G35" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="H35" s="23">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="F37" s="17">
-        <v>1200</v>
-      </c>
-      <c r="H37" s="18">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="19">
-        <v>46255.5</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F38" s="21">
-        <v>600</v>
-      </c>
-      <c r="G38" s="22">
-        <v>0.12083333333333333</v>
-      </c>
-      <c r="H38" s="23">
-        <v>72.5</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="19">
-        <v>46260.5</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F39" s="21">
-        <v>600</v>
-      </c>
-      <c r="G39" s="22">
-        <v>0.12083333333333333</v>
-      </c>
-      <c r="H39" s="23">
-        <v>72.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F41" s="17">
-        <v>600</v>
-      </c>
-      <c r="H41" s="18">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B42" s="19">
-        <v>46241.5</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F42" s="21">
-        <v>600</v>
-      </c>
-      <c r="G42" s="22">
-        <v>0.11666666666666667</v>
-      </c>
-      <c r="H42" s="23">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="F44" s="17">
-        <v>600</v>
-      </c>
-      <c r="H44" s="18">
+      <c r="H47" s="22">
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="19">
-        <v>46244.5</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E45" s="2" t="s">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="F45" s="21">
-        <v>600</v>
-      </c>
-      <c r="G45" s="22">
-        <v>0.15</v>
-      </c>
-      <c r="H45" s="23">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="F48" s="25">
-        <v>31275</v>
-      </c>
-      <c r="H48" s="26">
-        <v>3114.17</v>
+      <c r="F50" s="24">
+        <v>25200</v>
+      </c>
+      <c r="H50" s="25">
+        <v>5775</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="C14:H14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1475,1034 +1496,1034 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+    <row r="5" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="B5" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="14" t="s">
+      <c r="D5" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="J5" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="29" t="s">
+      <c r="K5" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="L5" s="28" t="s">
         <v>68</v>
-      </c>
-      <c r="L5" s="29" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="30">
+        <v>69</v>
+      </c>
+      <c r="B6" s="29">
         <v>46238.5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="31">
+        <v>35</v>
+      </c>
+      <c r="D6" s="30">
         <v>2</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="20">
         <v>1650</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="31">
         <v>1650</v>
       </c>
-      <c r="G6" s="33">
-        <v>0</v>
-      </c>
-      <c r="H6" s="21">
-        <v>0</v>
-      </c>
-      <c r="I6" s="34">
-        <v>0</v>
-      </c>
-      <c r="J6" s="30" t="s">
+      <c r="G6" s="32">
+        <v>0</v>
+      </c>
+      <c r="H6" s="20">
+        <v>0</v>
+      </c>
+      <c r="I6" s="33">
+        <v>0</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" s="33">
+        <v>0</v>
+      </c>
+      <c r="L6" s="34" t="s">
         <v>71</v>
-      </c>
-      <c r="K6" s="34">
-        <v>0</v>
-      </c>
-      <c r="L6" s="35" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="30">
+        <v>36</v>
+      </c>
+      <c r="B7" s="29">
         <v>46238.5</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="31">
+        <v>35</v>
+      </c>
+      <c r="D7" s="30">
         <v>8</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="20">
         <v>6600</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="31">
         <v>1800</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="32">
         <v>4800</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="20">
         <v>4800</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="22">
         <v>4943.52</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="29">
         <v>46245.5</v>
       </c>
-      <c r="K7" s="34">
-        <v>0</v>
-      </c>
-      <c r="L7" s="35" t="s">
-        <v>71</v>
+      <c r="K7" s="33">
+        <v>0</v>
+      </c>
+      <c r="L7" s="34" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="29">
+        <v>46238.5</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="30">
-        <v>46238.5</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="31">
+      <c r="D8" s="30">
         <v>2</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="20">
         <v>1650</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="31">
         <v>1650</v>
       </c>
-      <c r="G8" s="33">
-        <v>0</v>
-      </c>
-      <c r="H8" s="21">
-        <v>0</v>
-      </c>
-      <c r="I8" s="34">
-        <v>0</v>
-      </c>
-      <c r="J8" s="30" t="s">
+      <c r="G8" s="32">
+        <v>0</v>
+      </c>
+      <c r="H8" s="20">
+        <v>0</v>
+      </c>
+      <c r="I8" s="33">
+        <v>0</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K8" s="33">
+        <v>0</v>
+      </c>
+      <c r="L8" s="34" t="s">
         <v>71</v>
-      </c>
-      <c r="K8" s="34">
-        <v>0</v>
-      </c>
-      <c r="L8" s="35" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="30">
+        <v>52</v>
+      </c>
+      <c r="B9" s="29">
         <v>46241.5</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="31">
+        <v>51</v>
+      </c>
+      <c r="D9" s="30">
         <v>1</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="20">
         <v>825</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="31">
         <v>225</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="32">
         <v>600</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="20">
         <v>600</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="22">
         <v>617.94</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="29">
         <v>46241.5</v>
       </c>
-      <c r="K9" s="34">
-        <v>0</v>
-      </c>
-      <c r="L9" s="35" t="s">
-        <v>71</v>
+      <c r="K9" s="33">
+        <v>0</v>
+      </c>
+      <c r="L9" s="34" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="29">
+        <v>46245.5</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="30">
-        <v>46245.5</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="30">
+        <v>1</v>
+      </c>
+      <c r="E10" s="20">
+        <v>825</v>
+      </c>
+      <c r="F10" s="31">
+        <v>825</v>
+      </c>
+      <c r="G10" s="32">
+        <v>0</v>
+      </c>
+      <c r="H10" s="20">
+        <v>0</v>
+      </c>
+      <c r="I10" s="33">
+        <v>0</v>
+      </c>
+      <c r="J10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" s="33">
+        <v>0</v>
+      </c>
+      <c r="L10" s="34" t="s">
         <v>76</v>
-      </c>
-      <c r="D10" s="31">
-        <v>1</v>
-      </c>
-      <c r="E10" s="21">
-        <v>825</v>
-      </c>
-      <c r="F10" s="32">
-        <v>825</v>
-      </c>
-      <c r="G10" s="33">
-        <v>0</v>
-      </c>
-      <c r="H10" s="21">
-        <v>0</v>
-      </c>
-      <c r="I10" s="34">
-        <v>0</v>
-      </c>
-      <c r="J10" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="K10" s="34">
-        <v>0</v>
-      </c>
-      <c r="L10" s="35" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="30">
+        <v>77</v>
+      </c>
+      <c r="B11" s="29">
         <v>46245.5</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="31">
+        <v>75</v>
+      </c>
+      <c r="D11" s="30">
         <v>3</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="20">
         <v>2475</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="31">
         <v>675</v>
       </c>
-      <c r="G11" s="33">
+      <c r="G11" s="32">
         <v>1800</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="20">
         <v>1800</v>
       </c>
-      <c r="I11" s="34">
-        <v>0</v>
-      </c>
-      <c r="J11" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="K11" s="36">
+      <c r="I11" s="33">
+        <v>0</v>
+      </c>
+      <c r="J11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" s="35">
         <v>1800</v>
       </c>
-      <c r="L11" s="35" t="s">
-        <v>71</v>
+      <c r="L11" s="34" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="30">
+        <v>45</v>
+      </c>
+      <c r="B12" s="29">
         <v>46246.5</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="31">
+        <v>44</v>
+      </c>
+      <c r="D12" s="30">
         <v>3</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="20">
         <v>2475</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="31">
         <v>675</v>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="32">
         <v>1800</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="20">
         <v>1800</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="22">
         <v>1853.82</v>
       </c>
-      <c r="J12" s="30">
+      <c r="J12" s="29">
         <v>46246.5</v>
       </c>
-      <c r="K12" s="34">
-        <v>0</v>
-      </c>
-      <c r="L12" s="35" t="s">
-        <v>71</v>
+      <c r="K12" s="33">
+        <v>0</v>
+      </c>
+      <c r="L12" s="34" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="29">
+        <v>46248.5</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B13" s="30">
-        <v>46248.5</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="31">
+      <c r="D13" s="30">
         <v>1</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="20">
         <v>825</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="31">
         <v>825</v>
       </c>
-      <c r="G13" s="33">
-        <v>0</v>
-      </c>
-      <c r="H13" s="21">
-        <v>0</v>
-      </c>
-      <c r="I13" s="34">
-        <v>0</v>
-      </c>
-      <c r="J13" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="K13" s="34">
-        <v>0</v>
-      </c>
-      <c r="L13" s="35" t="s">
-        <v>77</v>
+      <c r="G13" s="32">
+        <v>0</v>
+      </c>
+      <c r="H13" s="20">
+        <v>0</v>
+      </c>
+      <c r="I13" s="33">
+        <v>0</v>
+      </c>
+      <c r="J13" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K13" s="33">
+        <v>0</v>
+      </c>
+      <c r="L13" s="34" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="29">
+        <v>46248.5</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B14" s="30">
-        <v>46248.5</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="31">
+      <c r="D14" s="30">
         <v>2</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="20">
         <v>1650</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="31">
         <v>1650</v>
       </c>
-      <c r="G14" s="33">
-        <v>0</v>
-      </c>
-      <c r="H14" s="21">
-        <v>0</v>
-      </c>
-      <c r="I14" s="34">
-        <v>0</v>
-      </c>
-      <c r="J14" s="30" t="s">
+      <c r="G14" s="32">
+        <v>0</v>
+      </c>
+      <c r="H14" s="20">
+        <v>0</v>
+      </c>
+      <c r="I14" s="33">
+        <v>0</v>
+      </c>
+      <c r="J14" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K14" s="33">
+        <v>0</v>
+      </c>
+      <c r="L14" s="34" t="s">
         <v>71</v>
-      </c>
-      <c r="K14" s="34">
-        <v>0</v>
-      </c>
-      <c r="L14" s="35" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="30">
+        <v>82</v>
+      </c>
+      <c r="B15" s="29">
         <v>46248.5</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="31">
+        <v>39</v>
+      </c>
+      <c r="D15" s="30">
         <v>4</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="20">
         <v>3300</v>
       </c>
-      <c r="F15" s="32">
+      <c r="F15" s="31">
         <v>3300</v>
       </c>
-      <c r="G15" s="33">
-        <v>0</v>
-      </c>
-      <c r="H15" s="21">
-        <v>0</v>
-      </c>
-      <c r="I15" s="34">
-        <v>0</v>
-      </c>
-      <c r="J15" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="K15" s="34">
-        <v>0</v>
-      </c>
-      <c r="L15" s="35" t="s">
-        <v>71</v>
+      <c r="G15" s="32">
+        <v>0</v>
+      </c>
+      <c r="H15" s="20">
+        <v>0</v>
+      </c>
+      <c r="I15" s="33">
+        <v>0</v>
+      </c>
+      <c r="J15" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K15" s="33">
+        <v>0</v>
+      </c>
+      <c r="L15" s="34" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="29">
+        <v>46251.5</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="30">
-        <v>46251.5</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" s="31">
+      <c r="D16" s="30">
         <v>1</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="20">
         <v>825</v>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="31">
         <v>225</v>
       </c>
-      <c r="G16" s="33">
+      <c r="G16" s="32">
         <v>600</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="20">
         <v>600</v>
       </c>
-      <c r="I16" s="34">
-        <v>0</v>
-      </c>
-      <c r="J16" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="K16" s="36">
+      <c r="I16" s="33">
+        <v>0</v>
+      </c>
+      <c r="J16" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K16" s="35">
         <v>600</v>
       </c>
-      <c r="L16" s="35" t="s">
-        <v>71</v>
+      <c r="L16" s="34" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B17" s="30">
+        <v>85</v>
+      </c>
+      <c r="B17" s="29">
         <v>46251.5</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="31">
+        <v>81</v>
+      </c>
+      <c r="D17" s="30">
         <v>8</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="20">
         <v>6600</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="31">
         <v>1800</v>
       </c>
-      <c r="G17" s="33">
+      <c r="G17" s="32">
         <v>4800</v>
       </c>
-      <c r="H17" s="21">
+      <c r="H17" s="20">
         <v>4800</v>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="22">
         <v>4800</v>
       </c>
-      <c r="J17" s="30">
+      <c r="J17" s="29">
         <v>46276.5</v>
       </c>
-      <c r="K17" s="34">
-        <v>0</v>
-      </c>
-      <c r="L17" s="35" t="s">
-        <v>71</v>
+      <c r="K17" s="33">
+        <v>0</v>
+      </c>
+      <c r="L17" s="34" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B18" s="30">
+        <v>86</v>
+      </c>
+      <c r="B18" s="29">
         <v>46251.5</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="31">
+        <v>39</v>
+      </c>
+      <c r="D18" s="30">
         <v>4</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="20">
         <v>3300</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="31">
         <v>900</v>
       </c>
-      <c r="G18" s="33">
+      <c r="G18" s="32">
         <v>2400</v>
       </c>
-      <c r="H18" s="21">
+      <c r="H18" s="20">
         <v>2400</v>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="22">
         <v>2400</v>
       </c>
-      <c r="J18" s="30">
+      <c r="J18" s="29">
         <v>46267.5</v>
       </c>
-      <c r="K18" s="34">
-        <v>0</v>
-      </c>
-      <c r="L18" s="35" t="s">
-        <v>71</v>
+      <c r="K18" s="33">
+        <v>0</v>
+      </c>
+      <c r="L18" s="34" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B19" s="30">
+        <v>87</v>
+      </c>
+      <c r="B19" s="29">
         <v>46252.5</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="31">
+        <v>53</v>
+      </c>
+      <c r="D19" s="30">
         <v>1</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="20">
         <v>825</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="31">
         <v>150</v>
       </c>
-      <c r="G19" s="33">
+      <c r="G19" s="32">
         <v>675</v>
       </c>
-      <c r="H19" s="21">
+      <c r="H19" s="20">
         <v>600</v>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="22">
         <v>675</v>
       </c>
-      <c r="J19" s="30">
+      <c r="J19" s="29">
         <v>46279.5</v>
       </c>
-      <c r="K19" s="34">
-        <v>0</v>
-      </c>
-      <c r="L19" s="35" t="s">
-        <v>71</v>
+      <c r="K19" s="33">
+        <v>0</v>
+      </c>
+      <c r="L19" s="34" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="30">
+        <v>88</v>
+      </c>
+      <c r="B20" s="29">
         <v>46253.5</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="31">
+        <v>39</v>
+      </c>
+      <c r="D20" s="30">
         <v>3</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="20">
         <v>2475</v>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="31">
         <v>2475</v>
       </c>
-      <c r="G20" s="33">
-        <v>0</v>
-      </c>
-      <c r="H20" s="21">
-        <v>0</v>
-      </c>
-      <c r="I20" s="34">
-        <v>0</v>
-      </c>
-      <c r="J20" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="K20" s="34">
-        <v>0</v>
-      </c>
-      <c r="L20" s="35" t="s">
-        <v>77</v>
+      <c r="G20" s="32">
+        <v>0</v>
+      </c>
+      <c r="H20" s="20">
+        <v>0</v>
+      </c>
+      <c r="I20" s="33">
+        <v>0</v>
+      </c>
+      <c r="J20" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K20" s="33">
+        <v>0</v>
+      </c>
+      <c r="L20" s="34" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" s="30">
+        <v>89</v>
+      </c>
+      <c r="B21" s="29">
         <v>46253.5</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" s="31">
+        <v>39</v>
+      </c>
+      <c r="D21" s="30">
         <v>1</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="20">
         <v>825</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="31">
         <v>225</v>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="32">
         <v>600</v>
       </c>
-      <c r="H21" s="21">
+      <c r="H21" s="20">
         <v>600</v>
       </c>
-      <c r="I21" s="34">
-        <v>0</v>
-      </c>
-      <c r="J21" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="K21" s="36">
+      <c r="I21" s="33">
+        <v>0</v>
+      </c>
+      <c r="J21" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K21" s="35">
         <v>600</v>
       </c>
-      <c r="L21" s="35" t="s">
-        <v>71</v>
+      <c r="L21" s="34" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="29">
+        <v>46254.5</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B22" s="30">
-        <v>46254.5</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" s="31">
+      <c r="D22" s="30">
         <v>2</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="20">
         <v>1650</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="31">
         <v>1650</v>
       </c>
-      <c r="G22" s="33">
-        <v>0</v>
-      </c>
-      <c r="H22" s="21">
-        <v>0</v>
-      </c>
-      <c r="I22" s="34">
-        <v>0</v>
-      </c>
-      <c r="J22" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="K22" s="34">
-        <v>0</v>
-      </c>
-      <c r="L22" s="35" t="s">
-        <v>77</v>
+      <c r="G22" s="32">
+        <v>0</v>
+      </c>
+      <c r="H22" s="20">
+        <v>0</v>
+      </c>
+      <c r="I22" s="33">
+        <v>0</v>
+      </c>
+      <c r="J22" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K22" s="33">
+        <v>0</v>
+      </c>
+      <c r="L22" s="34" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B23" s="30">
+        <v>92</v>
+      </c>
+      <c r="B23" s="29">
         <v>46254.5</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" s="31">
+        <v>91</v>
+      </c>
+      <c r="D23" s="30">
         <v>8</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="20">
         <v>6600</v>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="31">
         <v>1800</v>
       </c>
-      <c r="G23" s="33">
+      <c r="G23" s="32">
         <v>4800</v>
       </c>
-      <c r="H23" s="21">
+      <c r="H23" s="20">
         <v>4800</v>
       </c>
-      <c r="I23" s="34">
-        <v>0</v>
-      </c>
-      <c r="J23" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="K23" s="36">
+      <c r="I23" s="33">
+        <v>0</v>
+      </c>
+      <c r="J23" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K23" s="35">
         <v>4800</v>
       </c>
-      <c r="L23" s="35" t="s">
-        <v>71</v>
+      <c r="L23" s="34" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="29">
+        <v>46255.5</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="30">
-        <v>46255.5</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" s="31">
+      <c r="D24" s="30">
         <v>2</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="20">
         <v>1650</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="31">
         <v>1650</v>
       </c>
-      <c r="G24" s="33">
-        <v>0</v>
-      </c>
-      <c r="H24" s="21">
-        <v>0</v>
-      </c>
-      <c r="I24" s="34">
-        <v>0</v>
-      </c>
-      <c r="J24" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="K24" s="34">
-        <v>0</v>
-      </c>
-      <c r="L24" s="35" t="s">
-        <v>77</v>
+      <c r="G24" s="32">
+        <v>0</v>
+      </c>
+      <c r="H24" s="20">
+        <v>0</v>
+      </c>
+      <c r="I24" s="33">
+        <v>0</v>
+      </c>
+      <c r="J24" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K24" s="33">
+        <v>0</v>
+      </c>
+      <c r="L24" s="34" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" s="30">
+        <v>95</v>
+      </c>
+      <c r="B25" s="29">
         <v>46255.5</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" s="31">
+        <v>94</v>
+      </c>
+      <c r="D25" s="30">
         <v>8</v>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="20">
         <v>6600</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="31">
         <v>1800</v>
       </c>
-      <c r="G25" s="33">
+      <c r="G25" s="32">
         <v>4800</v>
       </c>
-      <c r="H25" s="21">
+      <c r="H25" s="20">
         <v>4800</v>
       </c>
-      <c r="I25" s="23">
+      <c r="I25" s="22">
         <v>4800</v>
       </c>
-      <c r="J25" s="30">
+      <c r="J25" s="29">
         <v>46267.5</v>
       </c>
-      <c r="K25" s="34">
-        <v>0</v>
-      </c>
-      <c r="L25" s="35" t="s">
-        <v>71</v>
+      <c r="K25" s="33">
+        <v>0</v>
+      </c>
+      <c r="L25" s="34" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="29">
+        <v>46255.5</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="30">
+        <v>5</v>
+      </c>
+      <c r="E26" s="20">
+        <v>3000</v>
+      </c>
+      <c r="F26" s="33">
+        <v>0</v>
+      </c>
+      <c r="G26" s="32">
+        <v>3000</v>
+      </c>
+      <c r="H26" s="20">
+        <v>3000</v>
+      </c>
+      <c r="I26" s="33">
+        <v>0</v>
+      </c>
+      <c r="J26" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K26" s="35">
+        <v>3000</v>
+      </c>
+      <c r="L26" s="34" t="s">
         <v>97</v>
-      </c>
-      <c r="B26" s="30">
-        <v>46255.5</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D26" s="31">
-        <v>5</v>
-      </c>
-      <c r="E26" s="21">
-        <v>3000</v>
-      </c>
-      <c r="F26" s="34">
-        <v>0</v>
-      </c>
-      <c r="G26" s="33">
-        <v>3000</v>
-      </c>
-      <c r="H26" s="21">
-        <v>3000</v>
-      </c>
-      <c r="I26" s="34">
-        <v>0</v>
-      </c>
-      <c r="J26" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="K26" s="36">
-        <v>3000</v>
-      </c>
-      <c r="L26" s="35" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B27" s="30">
+        <v>98</v>
+      </c>
+      <c r="B27" s="29">
         <v>46255.5</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27" s="31">
+        <v>48</v>
+      </c>
+      <c r="D27" s="30">
         <v>1</v>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="20">
         <v>825</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="31">
         <v>825</v>
       </c>
-      <c r="G27" s="33">
-        <v>0</v>
-      </c>
-      <c r="H27" s="21">
-        <v>0</v>
-      </c>
-      <c r="I27" s="34">
-        <v>0</v>
-      </c>
-      <c r="J27" s="30" t="s">
+      <c r="G27" s="32">
+        <v>0</v>
+      </c>
+      <c r="H27" s="20">
+        <v>0</v>
+      </c>
+      <c r="I27" s="33">
+        <v>0</v>
+      </c>
+      <c r="J27" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K27" s="33">
+        <v>0</v>
+      </c>
+      <c r="L27" s="34" t="s">
         <v>71</v>
-      </c>
-      <c r="K27" s="34">
-        <v>0</v>
-      </c>
-      <c r="L27" s="35" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="30">
+        <v>49</v>
+      </c>
+      <c r="B28" s="29">
         <v>46255.5</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="31">
+        <v>48</v>
+      </c>
+      <c r="D28" s="30">
         <v>1</v>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="20">
         <v>825</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="31">
         <v>225</v>
       </c>
-      <c r="G28" s="33">
+      <c r="G28" s="32">
         <v>600</v>
       </c>
-      <c r="H28" s="21">
+      <c r="H28" s="20">
         <v>600</v>
       </c>
-      <c r="I28" s="23">
+      <c r="I28" s="22">
         <v>617.94</v>
       </c>
-      <c r="J28" s="30">
+      <c r="J28" s="29">
         <v>46255.5</v>
       </c>
-      <c r="K28" s="34">
-        <v>0</v>
-      </c>
-      <c r="L28" s="35" t="s">
-        <v>71</v>
+      <c r="K28" s="33">
+        <v>0</v>
+      </c>
+      <c r="L28" s="34" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" s="29">
+        <v>46258.5</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B29" s="30">
-        <v>46258.5</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D29" s="31">
+      <c r="D29" s="30">
         <v>1</v>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="20">
         <v>825</v>
       </c>
-      <c r="F29" s="32">
+      <c r="F29" s="31">
         <v>825</v>
       </c>
-      <c r="G29" s="33">
-        <v>0</v>
-      </c>
-      <c r="H29" s="21">
-        <v>0</v>
-      </c>
-      <c r="I29" s="34">
-        <v>0</v>
-      </c>
-      <c r="J29" s="30" t="s">
+      <c r="G29" s="32">
+        <v>0</v>
+      </c>
+      <c r="H29" s="20">
+        <v>0</v>
+      </c>
+      <c r="I29" s="33">
+        <v>0</v>
+      </c>
+      <c r="J29" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K29" s="33">
+        <v>0</v>
+      </c>
+      <c r="L29" s="34" t="s">
         <v>71</v>
-      </c>
-      <c r="K29" s="34">
-        <v>0</v>
-      </c>
-      <c r="L29" s="35" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" s="29">
+        <v>46262.5</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="30">
-        <v>46262.5</v>
-      </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="30">
+        <v>1</v>
+      </c>
+      <c r="E30" s="20">
+        <v>825</v>
+      </c>
+      <c r="F30" s="31">
+        <v>825</v>
+      </c>
+      <c r="G30" s="32">
+        <v>0</v>
+      </c>
+      <c r="H30" s="20">
+        <v>0</v>
+      </c>
+      <c r="I30" s="33">
+        <v>0</v>
+      </c>
+      <c r="J30" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K30" s="33">
+        <v>0</v>
+      </c>
+      <c r="L30" s="34" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="D30" s="31">
-        <v>1</v>
-      </c>
-      <c r="E30" s="21">
-        <v>825</v>
-      </c>
-      <c r="F30" s="32">
-        <v>825</v>
-      </c>
-      <c r="G30" s="33">
-        <v>0</v>
-      </c>
-      <c r="H30" s="21">
-        <v>0</v>
-      </c>
-      <c r="I30" s="34">
-        <v>0</v>
-      </c>
-      <c r="J30" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="K30" s="34">
-        <v>0</v>
-      </c>
-      <c r="L30" s="35" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D32" s="38">
+      <c r="D32" s="37">
         <v>74</v>
       </c>
-      <c r="E32" s="33">
+      <c r="E32" s="32">
         <v>59925</v>
       </c>
-      <c r="F32" s="39">
+      <c r="F32" s="38">
         <v>28650</v>
       </c>
-      <c r="G32" s="40">
+      <c r="G32" s="39">
         <v>31275</v>
       </c>
-      <c r="H32" s="33">
+      <c r="H32" s="32">
         <v>31200</v>
       </c>
-      <c r="I32" s="41">
+      <c r="I32" s="40">
         <v>20708.219999999998</v>
       </c>
-      <c r="K32" s="42">
+      <c r="K32" s="41">
         <v>10800</v>
       </c>
     </row>
